--- a/Result/checksun_type/高爾夫球具業.xlsx
+++ b/Result/checksun_type/高爾夫球具業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>20.79</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>21.14</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>21.14</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>789.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>300.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>300.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>200.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>37.8473952601079</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>789</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>789.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>20.81</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>20.96</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>21.15</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>21.15</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>220.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>149.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>149.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>175.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>0</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-11.02743823016812</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>220</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>20.84</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>20.97</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>21.17</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21.17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>21.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>111.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>111.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>195.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>0</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-19.49050613662786</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>21</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>20.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>20.97</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>21.18</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>21.18</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>49.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>160.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>160.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>0</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-9.563085069547896</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>49</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>21.02</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>20.99</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>21.2</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>422.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>159.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>159.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>0</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>1.960483778764427</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>422</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>422.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>21.06</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>21.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>36.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>100.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>100.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>0</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-21.61157800145955</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>36</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>21.11</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>21.01</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>21.25</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>28.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>202.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>202.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>0</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-13.15696704458449</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>28</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>21.13</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>21.01</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>21.27</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>21.27</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>267.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>278.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>278.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>0</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>0.2480831454007557</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>267</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>267.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>21.11</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>21.02</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>21.28</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>21.28</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>44.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>0</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>0</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-6.217848124098936</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>44</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>21.03</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>21.02</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>21.29</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>21.29</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>128.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>0</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>0</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>8.66003035247644</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>128</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>21.03</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>21.01</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>21.31</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>21.31</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>544.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>0</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>0</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>20.60485566356718</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>544</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>544.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>67.12</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>64.13</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>61.72</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>64.13</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>61.72</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>25472.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>13762.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>13762.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>24641.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>15856.92</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>15856.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1473.265730244173</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>25472</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>25472.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>66.88</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>63.71</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>61.54</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>61.54</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>8043.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>12839.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>12839.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>28083.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>15637.14</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>15637.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-2147.755291842346</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>8043</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>8043.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>67.06</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>63.38</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>61.41</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>61.41</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>11010.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>19286.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>19286.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>33164.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>15682.88</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>15682.88</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-1167.213405131079</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>11010</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>11010.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,21 +7077,17 @@
           <t>67.17999999999999</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>63.07</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AM16" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="AO16" t="inlineStr">
         <is>
           <t>61.28</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>61.28</t>
-        </is>
-      </c>
       <c r="AP16" t="inlineStr">
         <is>
           <t>31.61</t>
@@ -7216,20 +7128,16 @@
           <t>11432.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>23750.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>23750.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>37810.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>15650.24</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>15650.24</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-42.64594536030563</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>11432</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>11432.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>67.36</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>62.79</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>61.17</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>61.17</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>12854.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>31130.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>31130.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>38847.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>15517.94</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>15517.94</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>1520.18778093224</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>12854</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>12854.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>67.1</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>62.49</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>61.06</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>61.06</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>20860.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>35520.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>35520.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>38231.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>15426.56</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>15426.56</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>3546.15782631687</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>20860</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>20860.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>62.12</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>60.93</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>60.93</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>40277.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>43327.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>43327.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>37171.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>15256.52</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>15256.52</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>5455.966540212172</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>40277</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>40277.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>66.1</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>61.78</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>60.8</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>33331.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>47043.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>47043.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>33816.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>14746.6</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>14746.6</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>5909.015897912162</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>33331</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>33331.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>65.26</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>61.41</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>60.65</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>60.65</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>48329.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>51870.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>51870.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>31007.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>14336.34</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>14336.34</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>7089.407269700998</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>48329</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>48329.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>61.05</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>60.5</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>34806.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>46565.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>46565.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>26612.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>13948.56</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>13948.56</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>6915.55896976716</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>34806</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>34806.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>62.7</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>60.77</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>60.37</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>60.37</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>59893.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>40941.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>40941.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>24373.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>13505.92</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>13505.92</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>7869.112863798564</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>59893</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>59893.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>25.69</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>26.47</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>25.83</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>25.83</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>797.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>515.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>515.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-78.82990423124306</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>797</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>797.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>25.8</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>26.48</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>446.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>471.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>471</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-111.6527166643008</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>446</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>446.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>25.92</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>26.48</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>78.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>435.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>435.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-116.9477088306584</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>78</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>26.19</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>26.49</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>467.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>0</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-80.90670803864555</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>467</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>467.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>26.46</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>26.49</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>789.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>0</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-68.20861019153267</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>789</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>789.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>26.69</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>25.81</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>25.81</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>575.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>0</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-82.13244861738826</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>575</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>575.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>26.96</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>26.44</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>25.8</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>26.44</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>25.8</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>269.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>0</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-76.16177320370366</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>269</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>269.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>27.26</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>26.4</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>25.78</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>25.78</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>0</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-12.10680834401489</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>0</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>27.35</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>26.33</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>25.76</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>25.76</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>683.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>948.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>948</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1159.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>849.94</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>849.9400000000001</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-12.10680834401489</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>683</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>683.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>27.43</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>26.26</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>25.73</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>25.73</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>427.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1133.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1133.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1126.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>846.68</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>846.6799999999999</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>13.88318674497373</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>427</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>427.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>27.4</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>26.21</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>25.7</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>777.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1362.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1362</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1101.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>848.5</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>848.5</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>77.94449448835144</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>777</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>777.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>71.84</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>72.81</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>71.2</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>72.81</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>71.2</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>6007.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>3975.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>3975.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>5226.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>9884.08</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>9884.08</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-1007.629459538829</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>6007</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>6007.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>71.52</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>72.88</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>71.08</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>71.08</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>3105.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>3817.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>3817.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>5350.8</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>9990.72</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>9990.719999999999</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-1202.131223237939</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>3105</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>3105.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>71.26</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>72.92</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>70.96</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>70.95999999999999</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>6515.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>4568.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>4568.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>6809.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>10092.02</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>10092.02</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-1126.129056263883</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>6515</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>6515.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>71.14</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>72.92</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>70.84</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>70.84</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>2752.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>5094.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>5094.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>6660.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>10198.06</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>10198.06</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-1342.692780005807</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>2752</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>2752.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>71.3</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>72.92</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>70.76</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>70.76000000000001</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1497.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>5808.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>5808</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>7118.6</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>10467.5</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>10467.5</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-1200.937643208348</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1497</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1497.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>71.64000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>72.89</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>70.67</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>72.89</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>70.67</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>5219.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>6478.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>6478</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>8354.2</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>10724.64</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>10724.64</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-821.0753890973956</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>5219</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>5219.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>72.18</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>72.82</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>70.58</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>72.81999999999999</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>70.58</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>6861.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>6884.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>6884</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>9685.9</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>11306.28</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>11306.28</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-647.8766193282718</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>6861</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>6861.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>72.94</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>72.76</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>70.43</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>72.76000000000001</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>70.43000000000001</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>9142.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>9050.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>9050.200000000001</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>10481.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>11334.88</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>11334.88</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-553.2399261106566</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>9142</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>9142.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>73.06</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>72.68</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>70.25</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>70.25</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>6321.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>8225.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>8225.799999999999</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>10498.4</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>11308.92</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>11308.92</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-642.6789384386811</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>6321</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>6321.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>73.24</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>72.61</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>70.08</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>70.08</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>4847.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>8429.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>8429.200000000001</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>10884.0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>12040.9</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>12040.9</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-445.246136820193</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>4847</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>4847.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>73.32000000000001</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>72.51</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>69.85</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>69.84999999999999</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>7249.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>10230.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>10230.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>11336.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>12307.36</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>12307.36</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>10.63094180694316</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>7249</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>7249.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>40.69</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>41.2</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>42.39</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>42.39</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>801944.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>779314.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>779314</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>923865.6</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>767710.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>767710</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-38479.10849819274</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>801944</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>801944.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>40.62</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>41.25</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>42.45</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>42.45</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>653914.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>822249.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>822249.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>949377.6</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>757849.12</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>757849.12</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-37514.9607102602</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>653914</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>653914.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>40.67</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>42.5</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>740294.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>921170.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>921170</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>992266.2</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>755626.24</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>755626.24</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-18937.42955927562</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>740294</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>740294.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>40.76</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>42.56</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>42.56</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>662798.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1080342.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1080342.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>1059655.6</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>744336.7</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>744336.7</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-976.7625736093614</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>662798</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>662798.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>40.91</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>42.64</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>42.64</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>1037620.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>1105853.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>1105853.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>1059696.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>734586.74</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>734586.74</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>33019.36035497149</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>1037620</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>1037620.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>41.07</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>42.7</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1016623.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>1068417.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>1068417.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>1067696.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>716447.34</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>716447.34</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>40246.48738312372</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1016623</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1016623.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>41.28</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>41.7</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>42.76</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>42.76</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1148515.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>1076505.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>1076505.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>1029919.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>706711.88</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>706711.88</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>51383.25858822942</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1148515</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1148515.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>41.4</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>41.78</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>42.83</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>42.83</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>1536158.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>1063362.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>1063362.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>1002812.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>689075.58</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>689075.58</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>51326.5296459439</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>1536158</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>1536158.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>41.5</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>41.87</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>42.88</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>42.88</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>790350.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>1038968.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>1038968.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>919814.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>660963.3</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>660963.3</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>7879.219383895048</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>790350</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>790350.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>41.55</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>41.93</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>42.92</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>42.92</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>850440.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>1013540.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>1013540.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>909999.9</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>649506.3</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>649506.3</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>25438.23260297196</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>850440</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>850440.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>41.51000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>42.01</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>42.97</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>42.97</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>1057064.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>1066974.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>1066974.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>946440.0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>656444.38</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>656444.38</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>43175.8146086901</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>1057064</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>1057064.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>238.6</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>243.6</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>250.99</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>243.6</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>250.99</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>54942243.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>59197652.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>59197652.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>78690413.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>82681246.84</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>82681246.84</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-3411494.063218117</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>54942243</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>54942243.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>235.9</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>243.4</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>251.19</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>251.19</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>43126575.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>61938984.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>61938984.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>82871637.3</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>83890010.46</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>83890010.45999999</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-2499433.970328555</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>43126575</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>43126575.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>234.9</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>243.5</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>251.63</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>251.63</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>78418020.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>84938435.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>84938435.40000001</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>83621581.8</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>85247737.8</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>85247737.8</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>158738.9470254034</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>78418020</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>78418020.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>234.7</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>243.62</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>252.01</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>243.62</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>252.01</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>49315909.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>86913845.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>86913845.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>86958592.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>85157649.34</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>85157649.34</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>169233.3308515847</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>49315909</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>49315909.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>236.5</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>244.45</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>252.6</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>244.45</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>252.6</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>70185515.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>95771935.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>95771935.40000001</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>86498593.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>86164352.74</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>86164352.73999999</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>3296264.581644282</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>70185515</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>70185515.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>240.3</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>245.2</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>253.31</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>245.2</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>253.31</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>68648903.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>98183174.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>98183174.59999999</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>82644139.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>86352714.72</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>86352714.72</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>5409699.133432284</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>68648903</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>68648903.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>245.3</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>245.88</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>254.1</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>245.88</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>254.1</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>158123830.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>103804290.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>103804290.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>79971834.4</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>87228771.0</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>87228771</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>8400324.809792534</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>158123830</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>158123830.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>249.2</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>246.52</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>254.76</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>246.52</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>254.76</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>88295069.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>82304728.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>82304728.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>68629123.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>85252416.16</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>85252416.16</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>2786036.282814607</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>88295069</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>88295069.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>251.3</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>246.9</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>255.22</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>255.22</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>93606360.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>87003339.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>87003339.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>64414727.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>85452720.26</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>85452720.26000001</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>2147775.769888476</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>93606360</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>93606360.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>252.1</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>247.22</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>255.64</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>247.22</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>255.64</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>82241711.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>77225252.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>77225252</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>64102438.9</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>84975550.64</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>84975550.64</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>590201.8667836934</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>82241711</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>82241711.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>250.6</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>246.98</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>255.89</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>246.98</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>255.89</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>96754481.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>67105104.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>67105104</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>64994581.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>84987340.86</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>84987340.86</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-438341.3828939646</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>96754481</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>96754481.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
